--- a/ZYQDManager/wwwroot/Templates/装箱单模板-报关.xlsx
+++ b/ZYQDManager/wwwroot/Templates/装箱单模板-报关.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\192.168.3.240\品质登记\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\JC_Project\ZYQDManager\ZYQDManager\wwwroot\Templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="46">
   <si>
     <t>美国 Vertilux 18046952+18047243 装箱单</t>
   </si>
@@ -169,6 +169,14 @@
   </si>
   <si>
     <t>不足托箱数</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>铭牌1类型</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>铭牌2类型</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -658,6 +666,8 @@
     <cellStyle name="표준 3" xfId="6"/>
     <cellStyle name="표준 3 2" xfId="7"/>
   </cellStyles>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
       <color rgb="FFFFFF00"/>
@@ -930,38 +940,38 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AH28"/>
+  <dimension ref="A1:AJ28"/>
   <sheetFormatPr defaultColWidth="9.125" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="2" width="30.75" style="47" customWidth="1"/>
     <col min="3" max="3" width="35.25" style="47" customWidth="1"/>
     <col min="4" max="4" width="34.875" style="47" customWidth="1"/>
     <col min="5" max="6" width="25.75" style="47" customWidth="1"/>
-    <col min="7" max="8" width="30.75" style="47" customWidth="1"/>
-    <col min="9" max="9" width="22.625" style="48" customWidth="1"/>
-    <col min="10" max="10" width="17.375" style="47" customWidth="1"/>
-    <col min="11" max="11" width="60" style="48" customWidth="1"/>
-    <col min="12" max="12" width="21.625" style="47" customWidth="1"/>
-    <col min="13" max="13" width="19.75" style="47" customWidth="1"/>
-    <col min="14" max="15" width="15.75" style="48" customWidth="1"/>
-    <col min="16" max="16" width="21.75" style="47" customWidth="1"/>
-    <col min="17" max="17" width="30.625" style="47" customWidth="1"/>
-    <col min="18" max="19" width="23.875" style="47" customWidth="1"/>
-    <col min="20" max="20" width="38" style="47" customWidth="1"/>
-    <col min="21" max="21" width="15.75" style="48" customWidth="1"/>
-    <col min="22" max="22" width="15.75" style="49" customWidth="1"/>
-    <col min="23" max="23" width="15.75" style="47" customWidth="1"/>
-    <col min="24" max="24" width="19.375" style="47" customWidth="1"/>
-    <col min="25" max="25" width="19.375" style="48" customWidth="1"/>
+    <col min="7" max="10" width="30.75" style="47" customWidth="1"/>
+    <col min="11" max="11" width="22.625" style="48" customWidth="1"/>
+    <col min="12" max="12" width="17.375" style="47" customWidth="1"/>
+    <col min="13" max="13" width="60" style="48" customWidth="1"/>
+    <col min="14" max="14" width="21.625" style="47" customWidth="1"/>
+    <col min="15" max="15" width="19.75" style="47" customWidth="1"/>
+    <col min="16" max="17" width="15.75" style="48" customWidth="1"/>
+    <col min="18" max="18" width="21.75" style="47" customWidth="1"/>
+    <col min="19" max="19" width="30.625" style="47" customWidth="1"/>
+    <col min="20" max="21" width="23.875" style="47" customWidth="1"/>
+    <col min="22" max="22" width="38" style="47" customWidth="1"/>
+    <col min="23" max="23" width="15.75" style="48" customWidth="1"/>
+    <col min="24" max="24" width="15.75" style="49" customWidth="1"/>
+    <col min="25" max="25" width="15.75" style="47" customWidth="1"/>
     <col min="26" max="26" width="19.375" style="47" customWidth="1"/>
-    <col min="27" max="31" width="15.75" style="48" customWidth="1"/>
-    <col min="32" max="32" width="15.75" style="51" customWidth="1"/>
-    <col min="33" max="34" width="15.75" style="1" customWidth="1"/>
-    <col min="35" max="35" width="18.125" style="1" customWidth="1"/>
-    <col min="36" max="16384" width="9.125" style="1"/>
+    <col min="27" max="27" width="19.375" style="48" customWidth="1"/>
+    <col min="28" max="28" width="19.375" style="47" customWidth="1"/>
+    <col min="29" max="33" width="15.75" style="48" customWidth="1"/>
+    <col min="34" max="34" width="15.75" style="51" customWidth="1"/>
+    <col min="35" max="36" width="15.75" style="1" customWidth="1"/>
+    <col min="37" max="37" width="18.125" style="1" customWidth="1"/>
+    <col min="38" max="16384" width="9.125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:34" ht="43.7" customHeight="1">
+    <row r="1" spans="1:36" ht="43.7" customHeight="1">
       <c r="A1" s="55" t="s">
         <v>0</v>
       </c>
@@ -998,8 +1008,10 @@
       <c r="AF1" s="55"/>
       <c r="AG1" s="55"/>
       <c r="AH1" s="55"/>
-    </row>
-    <row r="2" spans="1:34" s="6" customFormat="1" ht="37.700000000000003" customHeight="1">
+      <c r="AI1" s="55"/>
+      <c r="AJ1" s="55"/>
+    </row>
+    <row r="2" spans="1:36" s="6" customFormat="1" ht="37.700000000000003" customHeight="1">
       <c r="A2" s="56" t="s">
         <v>1</v>
       </c>
@@ -1011,45 +1023,47 @@
       <c r="G2" s="56"/>
       <c r="H2" s="56"/>
       <c r="I2" s="56"/>
-      <c r="J2" s="2"/>
-      <c r="K2" s="3" t="s">
+      <c r="J2" s="56"/>
+      <c r="K2" s="56"/>
+      <c r="L2" s="2"/>
+      <c r="M2" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="L2" s="4"/>
-      <c r="M2" s="3" t="s">
+      <c r="N2" s="4"/>
+      <c r="O2" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N2" s="57" t="s">
+      <c r="P2" s="57" t="s">
         <v>4</v>
       </c>
-      <c r="O2" s="57"/>
-      <c r="P2" s="57"/>
-      <c r="Q2" s="5" t="s">
+      <c r="Q2" s="57"/>
+      <c r="R2" s="57"/>
+      <c r="S2" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="R2" s="59"/>
-      <c r="S2" s="60"/>
-      <c r="T2" s="60"/>
-      <c r="U2" s="61"/>
-      <c r="V2" s="56" t="s">
+      <c r="T2" s="59"/>
+      <c r="U2" s="60"/>
+      <c r="V2" s="60"/>
+      <c r="W2" s="61"/>
+      <c r="X2" s="56" t="s">
         <v>6</v>
       </c>
-      <c r="W2" s="56"/>
-      <c r="X2" s="56"/>
-      <c r="Y2" s="58"/>
-      <c r="Z2" s="58"/>
+      <c r="Y2" s="56"/>
+      <c r="Z2" s="56"/>
       <c r="AA2" s="58"/>
       <c r="AB2" s="58"/>
-      <c r="AC2" s="5" t="s">
+      <c r="AC2" s="58"/>
+      <c r="AD2" s="58"/>
+      <c r="AE2" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="AD2" s="56"/>
-      <c r="AE2" s="56"/>
       <c r="AF2" s="56"/>
       <c r="AG2" s="56"/>
       <c r="AH2" s="56"/>
-    </row>
-    <row r="3" spans="1:34" s="11" customFormat="1" ht="61.35" customHeight="1">
+      <c r="AI2" s="56"/>
+      <c r="AJ2" s="56"/>
+    </row>
+    <row r="3" spans="1:36" s="11" customFormat="1" ht="61.35" customHeight="1">
       <c r="A3" s="7" t="s">
         <v>8</v>
       </c>
@@ -1072,88 +1086,94 @@
         <v>14</v>
       </c>
       <c r="H3" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="I3" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="I3" s="8" t="s">
+      <c r="J3" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="K3" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="J3" s="8" t="s">
+      <c r="L3" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="K3" s="8" t="s">
+      <c r="M3" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="L3" s="8" t="s">
+      <c r="N3" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="M3" s="7" t="s">
+      <c r="O3" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="N3" s="9" t="s">
+      <c r="P3" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="O3" s="9" t="s">
+      <c r="Q3" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="P3" s="7" t="s">
+      <c r="R3" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="Q3" s="7" t="s">
+      <c r="S3" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="R3" s="7" t="s">
+      <c r="T3" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="S3" s="7" t="s">
+      <c r="U3" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="T3" s="7" t="s">
+      <c r="V3" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="U3" s="7" t="s">
+      <c r="W3" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="V3" s="7" t="s">
+      <c r="X3" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="W3" s="7" t="s">
+      <c r="Y3" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="X3" s="9" t="s">
+      <c r="Z3" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="Y3" s="9" t="s">
+      <c r="AA3" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="Z3" s="9" t="s">
+      <c r="AB3" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="AA3" s="7" t="s">
+      <c r="AC3" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="AB3" s="9" t="s">
+      <c r="AD3" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="AC3" s="10" t="s">
+      <c r="AE3" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="AD3" s="9" t="s">
+      <c r="AF3" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="AE3" s="9" t="s">
+      <c r="AG3" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="AF3" s="9" t="s">
+      <c r="AH3" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="AG3" s="9" t="s">
+      <c r="AI3" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="AH3" s="9" t="s">
+      <c r="AJ3" s="9" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="4" spans="1:34" s="27" customFormat="1" ht="150.75" customHeight="1">
+    <row r="4" spans="1:36" s="27" customFormat="1" ht="150.75" customHeight="1">
       <c r="A4" s="12"/>
       <c r="B4" s="12"/>
       <c r="C4" s="13"/>
@@ -1162,34 +1182,36 @@
       <c r="F4" s="13"/>
       <c r="G4" s="13"/>
       <c r="H4" s="13"/>
-      <c r="I4" s="14"/>
-      <c r="J4" s="14"/>
-      <c r="K4" s="19"/>
-      <c r="L4" s="15"/>
-      <c r="M4" s="16"/>
-      <c r="N4" s="17"/>
-      <c r="O4" s="17"/>
-      <c r="P4" s="16"/>
-      <c r="Q4" s="18"/>
-      <c r="R4" s="18"/>
+      <c r="I4" s="13"/>
+      <c r="J4" s="13"/>
+      <c r="K4" s="14"/>
+      <c r="L4" s="14"/>
+      <c r="M4" s="19"/>
+      <c r="N4" s="15"/>
+      <c r="O4" s="16"/>
+      <c r="P4" s="17"/>
+      <c r="Q4" s="17"/>
+      <c r="R4" s="16"/>
       <c r="S4" s="18"/>
-      <c r="T4" s="19"/>
-      <c r="U4" s="20"/>
-      <c r="V4" s="21"/>
-      <c r="W4" s="22"/>
-      <c r="X4" s="23"/>
-      <c r="Y4" s="23"/>
-      <c r="Z4" s="21"/>
-      <c r="AA4" s="18"/>
-      <c r="AB4" s="18"/>
-      <c r="AC4" s="24"/>
-      <c r="AD4" s="25"/>
-      <c r="AE4" s="25"/>
+      <c r="T4" s="18"/>
+      <c r="U4" s="18"/>
+      <c r="V4" s="19"/>
+      <c r="W4" s="20"/>
+      <c r="X4" s="21"/>
+      <c r="Y4" s="22"/>
+      <c r="Z4" s="23"/>
+      <c r="AA4" s="23"/>
+      <c r="AB4" s="21"/>
+      <c r="AC4" s="18"/>
+      <c r="AD4" s="18"/>
+      <c r="AE4" s="24"/>
       <c r="AF4" s="25"/>
-      <c r="AG4" s="19"/>
-      <c r="AH4" s="26"/>
-    </row>
-    <row r="5" spans="1:34" s="38" customFormat="1" ht="55.35" customHeight="1">
+      <c r="AG4" s="25"/>
+      <c r="AH4" s="25"/>
+      <c r="AI4" s="19"/>
+      <c r="AJ4" s="26"/>
+    </row>
+    <row r="5" spans="1:36" s="38" customFormat="1" ht="55.35" customHeight="1">
       <c r="A5" s="28"/>
       <c r="B5" s="28"/>
       <c r="C5" s="28"/>
@@ -1198,50 +1220,52 @@
       <c r="F5" s="28"/>
       <c r="G5" s="28"/>
       <c r="H5" s="28"/>
-      <c r="I5" s="29" t="s">
+      <c r="I5" s="28"/>
+      <c r="J5" s="28"/>
+      <c r="K5" s="29" t="s">
         <v>39</v>
       </c>
-      <c r="J5" s="30"/>
-      <c r="K5" s="30"/>
-      <c r="L5" s="31">
+      <c r="L5" s="30"/>
+      <c r="M5" s="30"/>
+      <c r="N5" s="31">
         <v>0</v>
       </c>
-      <c r="M5" s="32"/>
-      <c r="N5" s="33">
+      <c r="O5" s="32"/>
+      <c r="P5" s="33">
         <v>0</v>
       </c>
-      <c r="O5" s="33">
+      <c r="Q5" s="33">
         <v>0</v>
       </c>
-      <c r="P5" s="32"/>
-      <c r="Q5" s="32"/>
       <c r="R5" s="32"/>
       <c r="S5" s="32"/>
       <c r="T5" s="32"/>
       <c r="U5" s="32"/>
       <c r="V5" s="32"/>
       <c r="W5" s="32"/>
-      <c r="X5" s="34">
-        <v>0</v>
-      </c>
-      <c r="Y5" s="34">
-        <v>0</v>
-      </c>
+      <c r="X5" s="32"/>
+      <c r="Y5" s="32"/>
       <c r="Z5" s="34">
         <v>0</v>
       </c>
-      <c r="AA5" s="32"/>
-      <c r="AB5" s="32">
+      <c r="AA5" s="34">
         <v>0</v>
       </c>
-      <c r="AC5" s="35"/>
-      <c r="AD5" s="36"/>
-      <c r="AE5" s="37"/>
+      <c r="AB5" s="34">
+        <v>0</v>
+      </c>
+      <c r="AC5" s="32"/>
+      <c r="AD5" s="32">
+        <v>0</v>
+      </c>
+      <c r="AE5" s="35"/>
       <c r="AF5" s="36"/>
-      <c r="AG5" s="36"/>
+      <c r="AG5" s="37"/>
       <c r="AH5" s="36"/>
-    </row>
-    <row r="6" spans="1:34" ht="24.75">
+      <c r="AI5" s="36"/>
+      <c r="AJ5" s="36"/>
+    </row>
+    <row r="6" spans="1:36" ht="24.75">
       <c r="A6" s="39"/>
       <c r="B6" s="39"/>
       <c r="C6" s="39"/>
@@ -1250,36 +1274,38 @@
       <c r="F6" s="39"/>
       <c r="G6" s="39"/>
       <c r="H6" s="39"/>
-      <c r="I6" s="40"/>
-      <c r="J6" s="41" t="s">
+      <c r="I6" s="39"/>
+      <c r="J6" s="39"/>
+      <c r="K6" s="40"/>
+      <c r="L6" s="41" t="s">
         <v>40</v>
       </c>
-      <c r="K6" s="40"/>
-      <c r="L6" s="39"/>
-      <c r="M6" s="39"/>
-      <c r="N6" s="40"/>
-      <c r="O6" s="40"/>
-      <c r="P6" s="42"/>
-      <c r="Q6" s="39"/>
-      <c r="R6" s="39"/>
+      <c r="M6" s="40"/>
+      <c r="N6" s="39"/>
+      <c r="O6" s="39"/>
+      <c r="P6" s="40"/>
+      <c r="Q6" s="40"/>
+      <c r="R6" s="42"/>
       <c r="S6" s="39"/>
       <c r="T6" s="39"/>
-      <c r="U6" s="40"/>
+      <c r="U6" s="39"/>
       <c r="V6" s="39"/>
       <c r="W6" s="40"/>
-      <c r="X6" s="40"/>
-      <c r="Y6" s="43"/>
-      <c r="Z6" s="43"/>
-      <c r="AA6" s="44"/>
-      <c r="AB6" s="44"/>
-      <c r="AC6" s="45"/>
-      <c r="AD6" s="43"/>
-      <c r="AE6" s="43"/>
+      <c r="X6" s="39"/>
+      <c r="Y6" s="40"/>
+      <c r="Z6" s="40"/>
+      <c r="AA6" s="43"/>
+      <c r="AB6" s="43"/>
+      <c r="AC6" s="44"/>
+      <c r="AD6" s="44"/>
+      <c r="AE6" s="45"/>
       <c r="AF6" s="43"/>
       <c r="AG6" s="43"/>
       <c r="AH6" s="43"/>
-    </row>
-    <row r="7" spans="1:34">
+      <c r="AI6" s="43"/>
+      <c r="AJ6" s="43"/>
+    </row>
+    <row r="7" spans="1:36">
       <c r="A7" s="39"/>
       <c r="B7" s="39"/>
       <c r="C7" s="39"/>
@@ -1288,34 +1314,36 @@
       <c r="F7" s="39"/>
       <c r="G7" s="39"/>
       <c r="H7" s="39"/>
-      <c r="I7" s="40"/>
-      <c r="J7" s="40"/>
+      <c r="I7" s="39"/>
+      <c r="J7" s="39"/>
       <c r="K7" s="40"/>
-      <c r="L7" s="39"/>
-      <c r="M7" s="39"/>
-      <c r="N7" s="40"/>
-      <c r="O7" s="40"/>
-      <c r="P7" s="42"/>
-      <c r="Q7" s="39"/>
-      <c r="R7" s="39"/>
+      <c r="L7" s="40"/>
+      <c r="M7" s="40"/>
+      <c r="N7" s="39"/>
+      <c r="O7" s="39"/>
+      <c r="P7" s="40"/>
+      <c r="Q7" s="40"/>
+      <c r="R7" s="42"/>
       <c r="S7" s="39"/>
       <c r="T7" s="39"/>
-      <c r="U7" s="40"/>
+      <c r="U7" s="39"/>
       <c r="V7" s="39"/>
       <c r="W7" s="40"/>
-      <c r="X7" s="40"/>
-      <c r="Y7" s="43"/>
-      <c r="Z7" s="43"/>
-      <c r="AA7" s="44"/>
-      <c r="AB7" s="44"/>
-      <c r="AC7" s="45"/>
-      <c r="AD7" s="43"/>
-      <c r="AE7" s="43"/>
+      <c r="X7" s="39"/>
+      <c r="Y7" s="40"/>
+      <c r="Z7" s="40"/>
+      <c r="AA7" s="43"/>
+      <c r="AB7" s="43"/>
+      <c r="AC7" s="44"/>
+      <c r="AD7" s="44"/>
+      <c r="AE7" s="45"/>
       <c r="AF7" s="43"/>
       <c r="AG7" s="43"/>
       <c r="AH7" s="43"/>
-    </row>
-    <row r="8" spans="1:34">
+      <c r="AI7" s="43"/>
+      <c r="AJ7" s="43"/>
+    </row>
+    <row r="8" spans="1:36">
       <c r="A8" s="39"/>
       <c r="B8" s="39"/>
       <c r="C8" s="39"/>
@@ -1324,34 +1352,36 @@
       <c r="F8" s="39"/>
       <c r="G8" s="39"/>
       <c r="H8" s="39"/>
-      <c r="I8" s="40"/>
-      <c r="J8" s="40"/>
+      <c r="I8" s="39"/>
+      <c r="J8" s="39"/>
       <c r="K8" s="40"/>
-      <c r="L8" s="39"/>
-      <c r="M8" s="39"/>
-      <c r="N8" s="40"/>
-      <c r="O8" s="40"/>
-      <c r="P8" s="42"/>
-      <c r="Q8" s="39"/>
-      <c r="R8" s="39"/>
+      <c r="L8" s="40"/>
+      <c r="M8" s="40"/>
+      <c r="N8" s="39"/>
+      <c r="O8" s="39"/>
+      <c r="P8" s="40"/>
+      <c r="Q8" s="40"/>
+      <c r="R8" s="42"/>
       <c r="S8" s="39"/>
       <c r="T8" s="39"/>
-      <c r="U8" s="40"/>
+      <c r="U8" s="39"/>
       <c r="V8" s="39"/>
       <c r="W8" s="40"/>
-      <c r="X8" s="40"/>
-      <c r="Y8" s="43"/>
-      <c r="Z8" s="43"/>
-      <c r="AA8" s="44"/>
-      <c r="AB8" s="44"/>
-      <c r="AC8" s="45"/>
-      <c r="AD8" s="43"/>
-      <c r="AE8" s="43"/>
+      <c r="X8" s="39"/>
+      <c r="Y8" s="40"/>
+      <c r="Z8" s="40"/>
+      <c r="AA8" s="43"/>
+      <c r="AB8" s="43"/>
+      <c r="AC8" s="44"/>
+      <c r="AD8" s="44"/>
+      <c r="AE8" s="45"/>
       <c r="AF8" s="43"/>
       <c r="AG8" s="43"/>
       <c r="AH8" s="43"/>
-    </row>
-    <row r="9" spans="1:34" ht="14.45" customHeight="1">
+      <c r="AI8" s="43"/>
+      <c r="AJ8" s="43"/>
+    </row>
+    <row r="9" spans="1:36" ht="14.45" customHeight="1">
       <c r="A9" s="39"/>
       <c r="B9" s="39"/>
       <c r="C9" s="39"/>
@@ -1360,34 +1390,36 @@
       <c r="F9" s="39"/>
       <c r="G9" s="39"/>
       <c r="H9" s="39"/>
-      <c r="I9" s="40"/>
-      <c r="J9" s="40"/>
-      <c r="K9" s="54"/>
-      <c r="L9" s="54"/>
+      <c r="I9" s="39"/>
+      <c r="J9" s="39"/>
+      <c r="K9" s="40"/>
+      <c r="L9" s="40"/>
       <c r="M9" s="54"/>
-      <c r="N9" s="40"/>
-      <c r="O9" s="40"/>
-      <c r="P9" s="42"/>
-      <c r="Q9" s="39"/>
-      <c r="R9" s="39"/>
+      <c r="N9" s="54"/>
+      <c r="O9" s="54"/>
+      <c r="P9" s="40"/>
+      <c r="Q9" s="40"/>
+      <c r="R9" s="42"/>
       <c r="S9" s="39"/>
       <c r="T9" s="39"/>
-      <c r="U9" s="40"/>
+      <c r="U9" s="39"/>
       <c r="V9" s="39"/>
       <c r="W9" s="40"/>
-      <c r="X9" s="40"/>
-      <c r="Y9" s="43"/>
-      <c r="Z9" s="43"/>
-      <c r="AA9" s="44"/>
-      <c r="AB9" s="44"/>
-      <c r="AC9" s="45"/>
-      <c r="AD9" s="43"/>
-      <c r="AE9" s="43"/>
+      <c r="X9" s="39"/>
+      <c r="Y9" s="40"/>
+      <c r="Z9" s="40"/>
+      <c r="AA9" s="43"/>
+      <c r="AB9" s="43"/>
+      <c r="AC9" s="44"/>
+      <c r="AD9" s="44"/>
+      <c r="AE9" s="45"/>
       <c r="AF9" s="43"/>
       <c r="AG9" s="43"/>
       <c r="AH9" s="43"/>
-    </row>
-    <row r="10" spans="1:34" ht="14.45" customHeight="1">
+      <c r="AI9" s="43"/>
+      <c r="AJ9" s="43"/>
+    </row>
+    <row r="10" spans="1:36" ht="14.45" customHeight="1">
       <c r="A10" s="39"/>
       <c r="B10" s="39"/>
       <c r="C10" s="39"/>
@@ -1396,34 +1428,36 @@
       <c r="F10" s="39"/>
       <c r="G10" s="39"/>
       <c r="H10" s="39"/>
-      <c r="I10" s="40"/>
-      <c r="J10" s="40"/>
-      <c r="K10" s="54"/>
-      <c r="L10" s="54"/>
+      <c r="I10" s="39"/>
+      <c r="J10" s="39"/>
+      <c r="K10" s="40"/>
+      <c r="L10" s="40"/>
       <c r="M10" s="54"/>
-      <c r="N10" s="40"/>
-      <c r="O10" s="40"/>
-      <c r="P10" s="42"/>
-      <c r="Q10" s="39"/>
-      <c r="R10" s="39"/>
+      <c r="N10" s="54"/>
+      <c r="O10" s="54"/>
+      <c r="P10" s="40"/>
+      <c r="Q10" s="40"/>
+      <c r="R10" s="42"/>
       <c r="S10" s="39"/>
       <c r="T10" s="39"/>
-      <c r="U10" s="40"/>
+      <c r="U10" s="39"/>
       <c r="V10" s="39"/>
       <c r="W10" s="40"/>
-      <c r="X10" s="40"/>
-      <c r="Y10" s="43"/>
-      <c r="Z10" s="43"/>
-      <c r="AA10" s="44"/>
-      <c r="AB10" s="44"/>
-      <c r="AC10" s="45"/>
-      <c r="AD10" s="43"/>
-      <c r="AE10" s="43"/>
+      <c r="X10" s="39"/>
+      <c r="Y10" s="40"/>
+      <c r="Z10" s="40"/>
+      <c r="AA10" s="43"/>
+      <c r="AB10" s="43"/>
+      <c r="AC10" s="44"/>
+      <c r="AD10" s="44"/>
+      <c r="AE10" s="45"/>
       <c r="AF10" s="43"/>
       <c r="AG10" s="43"/>
       <c r="AH10" s="43"/>
-    </row>
-    <row r="11" spans="1:34" ht="14.45" customHeight="1">
+      <c r="AI10" s="43"/>
+      <c r="AJ10" s="43"/>
+    </row>
+    <row r="11" spans="1:36" ht="14.45" customHeight="1">
       <c r="A11" s="39"/>
       <c r="B11" s="39"/>
       <c r="C11" s="39"/>
@@ -1432,34 +1466,36 @@
       <c r="F11" s="39"/>
       <c r="G11" s="39"/>
       <c r="H11" s="39"/>
-      <c r="I11" s="40"/>
-      <c r="J11" s="40"/>
-      <c r="K11" s="54"/>
-      <c r="L11" s="54"/>
+      <c r="I11" s="39"/>
+      <c r="J11" s="39"/>
+      <c r="K11" s="40"/>
+      <c r="L11" s="40"/>
       <c r="M11" s="54"/>
-      <c r="N11" s="40"/>
-      <c r="O11" s="40"/>
-      <c r="P11" s="42"/>
-      <c r="Q11" s="39"/>
-      <c r="R11" s="39"/>
+      <c r="N11" s="54"/>
+      <c r="O11" s="54"/>
+      <c r="P11" s="40"/>
+      <c r="Q11" s="40"/>
+      <c r="R11" s="42"/>
       <c r="S11" s="39"/>
       <c r="T11" s="39"/>
-      <c r="U11" s="40"/>
+      <c r="U11" s="39"/>
       <c r="V11" s="39"/>
       <c r="W11" s="40"/>
-      <c r="X11" s="40"/>
-      <c r="Y11" s="43"/>
-      <c r="Z11" s="43"/>
-      <c r="AA11" s="44"/>
-      <c r="AB11" s="44"/>
-      <c r="AC11" s="45"/>
-      <c r="AD11" s="43"/>
-      <c r="AE11" s="43"/>
+      <c r="X11" s="39"/>
+      <c r="Y11" s="40"/>
+      <c r="Z11" s="40"/>
+      <c r="AA11" s="43"/>
+      <c r="AB11" s="43"/>
+      <c r="AC11" s="44"/>
+      <c r="AD11" s="44"/>
+      <c r="AE11" s="45"/>
       <c r="AF11" s="43"/>
       <c r="AG11" s="43"/>
       <c r="AH11" s="43"/>
-    </row>
-    <row r="12" spans="1:34" ht="14.45" customHeight="1">
+      <c r="AI11" s="43"/>
+      <c r="AJ11" s="43"/>
+    </row>
+    <row r="12" spans="1:36" ht="14.45" customHeight="1">
       <c r="A12" s="39"/>
       <c r="B12" s="39"/>
       <c r="C12" s="39"/>
@@ -1468,34 +1504,36 @@
       <c r="F12" s="39"/>
       <c r="G12" s="39"/>
       <c r="H12" s="39"/>
-      <c r="I12" s="40"/>
-      <c r="J12" s="40"/>
-      <c r="K12" s="54"/>
-      <c r="L12" s="54"/>
+      <c r="I12" s="39"/>
+      <c r="J12" s="39"/>
+      <c r="K12" s="40"/>
+      <c r="L12" s="40"/>
       <c r="M12" s="54"/>
-      <c r="N12" s="40"/>
-      <c r="O12" s="40"/>
-      <c r="P12" s="42"/>
-      <c r="Q12" s="39"/>
-      <c r="R12" s="39"/>
+      <c r="N12" s="54"/>
+      <c r="O12" s="54"/>
+      <c r="P12" s="40"/>
+      <c r="Q12" s="40"/>
+      <c r="R12" s="42"/>
       <c r="S12" s="39"/>
       <c r="T12" s="39"/>
-      <c r="U12" s="40"/>
+      <c r="U12" s="39"/>
       <c r="V12" s="39"/>
       <c r="W12" s="40"/>
-      <c r="X12" s="40"/>
-      <c r="Y12" s="43"/>
-      <c r="Z12" s="43"/>
-      <c r="AA12" s="44"/>
-      <c r="AB12" s="44"/>
-      <c r="AC12" s="45"/>
-      <c r="AD12" s="43"/>
-      <c r="AE12" s="43"/>
+      <c r="X12" s="39"/>
+      <c r="Y12" s="40"/>
+      <c r="Z12" s="40"/>
+      <c r="AA12" s="43"/>
+      <c r="AB12" s="43"/>
+      <c r="AC12" s="44"/>
+      <c r="AD12" s="44"/>
+      <c r="AE12" s="45"/>
       <c r="AF12" s="43"/>
       <c r="AG12" s="43"/>
       <c r="AH12" s="43"/>
-    </row>
-    <row r="13" spans="1:34" ht="14.45" customHeight="1">
+      <c r="AI12" s="43"/>
+      <c r="AJ12" s="43"/>
+    </row>
+    <row r="13" spans="1:36" ht="14.45" customHeight="1">
       <c r="A13" s="39"/>
       <c r="B13" s="39"/>
       <c r="C13" s="39"/>
@@ -1504,34 +1542,36 @@
       <c r="F13" s="39"/>
       <c r="G13" s="39"/>
       <c r="H13" s="39"/>
-      <c r="I13" s="40"/>
-      <c r="J13" s="40"/>
-      <c r="K13" s="54"/>
-      <c r="L13" s="54"/>
+      <c r="I13" s="39"/>
+      <c r="J13" s="39"/>
+      <c r="K13" s="40"/>
+      <c r="L13" s="40"/>
       <c r="M13" s="54"/>
-      <c r="N13" s="40"/>
-      <c r="O13" s="40"/>
-      <c r="P13" s="42"/>
-      <c r="Q13" s="39"/>
-      <c r="R13" s="39"/>
+      <c r="N13" s="54"/>
+      <c r="O13" s="54"/>
+      <c r="P13" s="40"/>
+      <c r="Q13" s="40"/>
+      <c r="R13" s="42"/>
       <c r="S13" s="39"/>
       <c r="T13" s="39"/>
-      <c r="U13" s="40"/>
+      <c r="U13" s="39"/>
       <c r="V13" s="39"/>
       <c r="W13" s="40"/>
-      <c r="X13" s="40"/>
-      <c r="Y13" s="43"/>
-      <c r="Z13" s="43"/>
-      <c r="AA13" s="44"/>
-      <c r="AB13" s="44"/>
-      <c r="AC13" s="45"/>
+      <c r="X13" s="39"/>
+      <c r="Y13" s="40"/>
+      <c r="Z13" s="40"/>
+      <c r="AA13" s="43"/>
+      <c r="AB13" s="43"/>
+      <c r="AC13" s="44"/>
       <c r="AD13" s="44"/>
-      <c r="AE13" s="44"/>
-      <c r="AF13" s="46"/>
-      <c r="AG13" s="43"/>
-      <c r="AH13" s="43"/>
-    </row>
-    <row r="14" spans="1:34">
+      <c r="AE13" s="45"/>
+      <c r="AF13" s="44"/>
+      <c r="AG13" s="44"/>
+      <c r="AH13" s="46"/>
+      <c r="AI13" s="43"/>
+      <c r="AJ13" s="43"/>
+    </row>
+    <row r="14" spans="1:36">
       <c r="A14" s="39"/>
       <c r="B14" s="39"/>
       <c r="C14" s="39"/>
@@ -1540,34 +1580,36 @@
       <c r="F14" s="39"/>
       <c r="G14" s="39"/>
       <c r="H14" s="39"/>
-      <c r="I14" s="40"/>
-      <c r="J14" s="40"/>
+      <c r="I14" s="39"/>
+      <c r="J14" s="39"/>
       <c r="K14" s="40"/>
-      <c r="L14" s="39"/>
-      <c r="M14" s="39"/>
-      <c r="N14" s="40"/>
-      <c r="O14" s="40"/>
-      <c r="P14" s="42"/>
-      <c r="Q14" s="39"/>
-      <c r="R14" s="39"/>
+      <c r="L14" s="40"/>
+      <c r="M14" s="40"/>
+      <c r="N14" s="39"/>
+      <c r="O14" s="39"/>
+      <c r="P14" s="40"/>
+      <c r="Q14" s="40"/>
+      <c r="R14" s="42"/>
       <c r="S14" s="39"/>
       <c r="T14" s="39"/>
-      <c r="U14" s="40"/>
+      <c r="U14" s="39"/>
       <c r="V14" s="39"/>
       <c r="W14" s="40"/>
-      <c r="X14" s="40"/>
-      <c r="Y14" s="43"/>
-      <c r="Z14" s="43"/>
-      <c r="AA14" s="44"/>
-      <c r="AB14" s="44"/>
-      <c r="AC14" s="45"/>
+      <c r="X14" s="39"/>
+      <c r="Y14" s="40"/>
+      <c r="Z14" s="40"/>
+      <c r="AA14" s="43"/>
+      <c r="AB14" s="43"/>
+      <c r="AC14" s="44"/>
       <c r="AD14" s="44"/>
-      <c r="AE14" s="44"/>
-      <c r="AF14" s="46"/>
-      <c r="AG14" s="43"/>
-      <c r="AH14" s="43"/>
-    </row>
-    <row r="15" spans="1:34">
+      <c r="AE14" s="45"/>
+      <c r="AF14" s="44"/>
+      <c r="AG14" s="44"/>
+      <c r="AH14" s="46"/>
+      <c r="AI14" s="43"/>
+      <c r="AJ14" s="43"/>
+    </row>
+    <row r="15" spans="1:36">
       <c r="A15" s="39"/>
       <c r="B15" s="39"/>
       <c r="C15" s="39"/>
@@ -1576,34 +1618,36 @@
       <c r="F15" s="39"/>
       <c r="G15" s="39"/>
       <c r="H15" s="39"/>
-      <c r="I15" s="40"/>
-      <c r="J15" s="40"/>
+      <c r="I15" s="39"/>
+      <c r="J15" s="39"/>
       <c r="K15" s="40"/>
-      <c r="L15" s="39"/>
-      <c r="M15" s="39"/>
-      <c r="N15" s="40"/>
-      <c r="O15" s="40"/>
-      <c r="P15" s="42"/>
-      <c r="Q15" s="39"/>
-      <c r="R15" s="39"/>
+      <c r="L15" s="40"/>
+      <c r="M15" s="40"/>
+      <c r="N15" s="39"/>
+      <c r="O15" s="39"/>
+      <c r="P15" s="40"/>
+      <c r="Q15" s="40"/>
+      <c r="R15" s="42"/>
       <c r="S15" s="39"/>
       <c r="T15" s="39"/>
-      <c r="U15" s="40"/>
+      <c r="U15" s="39"/>
       <c r="V15" s="39"/>
       <c r="W15" s="40"/>
-      <c r="X15" s="40"/>
-      <c r="Y15" s="43"/>
-      <c r="Z15" s="43"/>
-      <c r="AA15" s="44"/>
-      <c r="AB15" s="44"/>
-      <c r="AC15" s="45"/>
+      <c r="X15" s="39"/>
+      <c r="Y15" s="40"/>
+      <c r="Z15" s="40"/>
+      <c r="AA15" s="43"/>
+      <c r="AB15" s="43"/>
+      <c r="AC15" s="44"/>
       <c r="AD15" s="44"/>
-      <c r="AE15" s="44"/>
-      <c r="AF15" s="46"/>
-      <c r="AG15" s="43"/>
-      <c r="AH15" s="43"/>
-    </row>
-    <row r="16" spans="1:34">
+      <c r="AE15" s="45"/>
+      <c r="AF15" s="44"/>
+      <c r="AG15" s="44"/>
+      <c r="AH15" s="46"/>
+      <c r="AI15" s="43"/>
+      <c r="AJ15" s="43"/>
+    </row>
+    <row r="16" spans="1:36">
       <c r="A16" s="1"/>
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
@@ -1613,19 +1657,21 @@
       <c r="G16" s="1"/>
       <c r="H16" s="1"/>
       <c r="I16" s="1"/>
-      <c r="N16" s="47"/>
-      <c r="O16" s="47"/>
-      <c r="U16" s="47"/>
-      <c r="V16" s="47"/>
-      <c r="Y16" s="47"/>
+      <c r="J16" s="1"/>
+      <c r="K16" s="1"/>
+      <c r="P16" s="47"/>
+      <c r="Q16" s="47"/>
+      <c r="W16" s="47"/>
+      <c r="X16" s="47"/>
       <c r="AA16" s="47"/>
-      <c r="AB16" s="47"/>
-      <c r="AC16" s="1"/>
-      <c r="AD16" s="1"/>
+      <c r="AC16" s="47"/>
+      <c r="AD16" s="47"/>
       <c r="AE16" s="1"/>
       <c r="AF16" s="1"/>
-    </row>
-    <row r="17" spans="1:32">
+      <c r="AG16" s="1"/>
+      <c r="AH16" s="1"/>
+    </row>
+    <row r="17" spans="1:34">
       <c r="A17" s="1"/>
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
@@ -1635,15 +1681,17 @@
       <c r="G17" s="1"/>
       <c r="H17" s="1"/>
       <c r="I17" s="1"/>
-      <c r="J17" s="48"/>
+      <c r="J17" s="1"/>
+      <c r="K17" s="1"/>
       <c r="L17" s="48"/>
-      <c r="M17" s="48"/>
-      <c r="AC17" s="1"/>
-      <c r="AD17" s="1"/>
+      <c r="N17" s="48"/>
+      <c r="O17" s="48"/>
       <c r="AE17" s="1"/>
       <c r="AF17" s="1"/>
-    </row>
-    <row r="18" spans="1:32">
+      <c r="AG17" s="1"/>
+      <c r="AH17" s="1"/>
+    </row>
+    <row r="18" spans="1:34">
       <c r="A18" s="1"/>
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
@@ -1653,9 +1701,9 @@
       <c r="G18" s="1"/>
       <c r="H18" s="1"/>
       <c r="I18" s="1"/>
-      <c r="J18" s="48"/>
-      <c r="L18" s="50"/>
-      <c r="M18" s="50"/>
+      <c r="J18" s="1"/>
+      <c r="K18" s="1"/>
+      <c r="L18" s="48"/>
       <c r="N18" s="50"/>
       <c r="O18" s="50"/>
       <c r="P18" s="50"/>
@@ -1671,12 +1719,14 @@
       <c r="Z18" s="50"/>
       <c r="AA18" s="50"/>
       <c r="AB18" s="50"/>
-      <c r="AC18" s="1"/>
-      <c r="AD18" s="1"/>
+      <c r="AC18" s="50"/>
+      <c r="AD18" s="50"/>
       <c r="AE18" s="1"/>
       <c r="AF18" s="1"/>
-    </row>
-    <row r="19" spans="1:32">
+      <c r="AG18" s="1"/>
+      <c r="AH18" s="1"/>
+    </row>
+    <row r="19" spans="1:34">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
@@ -1686,16 +1736,18 @@
       <c r="G19" s="1"/>
       <c r="H19" s="1"/>
       <c r="I19" s="1"/>
-      <c r="J19" s="48"/>
+      <c r="J19" s="1"/>
+      <c r="K19" s="1"/>
       <c r="L19" s="48"/>
-      <c r="M19" s="48"/>
-      <c r="Z19" s="48"/>
-      <c r="AC19" s="1"/>
-      <c r="AD19" s="1"/>
+      <c r="N19" s="48"/>
+      <c r="O19" s="48"/>
+      <c r="AB19" s="48"/>
       <c r="AE19" s="1"/>
       <c r="AF19" s="1"/>
-    </row>
-    <row r="20" spans="1:32">
+      <c r="AG19" s="1"/>
+      <c r="AH19" s="1"/>
+    </row>
+    <row r="20" spans="1:34">
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
@@ -1705,15 +1757,17 @@
       <c r="G20" s="1"/>
       <c r="H20" s="1"/>
       <c r="I20" s="1"/>
-      <c r="J20" s="48"/>
+      <c r="J20" s="1"/>
+      <c r="K20" s="1"/>
       <c r="L20" s="48"/>
-      <c r="M20" s="48"/>
-      <c r="AC20" s="1"/>
-      <c r="AD20" s="1"/>
+      <c r="N20" s="48"/>
+      <c r="O20" s="48"/>
       <c r="AE20" s="1"/>
       <c r="AF20" s="1"/>
-    </row>
-    <row r="21" spans="1:32">
+      <c r="AG20" s="1"/>
+      <c r="AH20" s="1"/>
+    </row>
+    <row r="21" spans="1:34">
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
@@ -1723,15 +1777,17 @@
       <c r="G21" s="1"/>
       <c r="H21" s="1"/>
       <c r="I21" s="1"/>
-      <c r="J21" s="48"/>
+      <c r="J21" s="1"/>
+      <c r="K21" s="1"/>
       <c r="L21" s="48"/>
-      <c r="M21" s="48"/>
-      <c r="AC21" s="1"/>
-      <c r="AD21" s="1"/>
+      <c r="N21" s="48"/>
+      <c r="O21" s="48"/>
       <c r="AE21" s="1"/>
       <c r="AF21" s="1"/>
-    </row>
-    <row r="22" spans="1:32">
+      <c r="AG21" s="1"/>
+      <c r="AH21" s="1"/>
+    </row>
+    <row r="22" spans="1:34">
       <c r="A22" s="1"/>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
@@ -1741,15 +1797,17 @@
       <c r="G22" s="1"/>
       <c r="H22" s="1"/>
       <c r="I22" s="1"/>
-      <c r="J22" s="48"/>
+      <c r="J22" s="1"/>
+      <c r="K22" s="1"/>
       <c r="L22" s="48"/>
-      <c r="M22" s="48"/>
-      <c r="AC22" s="1"/>
-      <c r="AD22" s="1"/>
+      <c r="N22" s="48"/>
+      <c r="O22" s="48"/>
       <c r="AE22" s="1"/>
       <c r="AF22" s="1"/>
-    </row>
-    <row r="23" spans="1:32">
+      <c r="AG22" s="1"/>
+      <c r="AH22" s="1"/>
+    </row>
+    <row r="23" spans="1:34">
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
@@ -1759,24 +1817,26 @@
       <c r="G23" s="1"/>
       <c r="H23" s="1"/>
       <c r="I23" s="1"/>
-      <c r="J23" s="48"/>
+      <c r="J23" s="1"/>
+      <c r="K23" s="1"/>
       <c r="L23" s="48"/>
-      <c r="M23" s="48"/>
-      <c r="P23" s="48"/>
-      <c r="Q23" s="48"/>
+      <c r="N23" s="48"/>
+      <c r="O23" s="48"/>
       <c r="R23" s="48"/>
       <c r="S23" s="48"/>
       <c r="T23" s="48"/>
+      <c r="U23" s="48"/>
       <c r="V23" s="48"/>
-      <c r="W23" s="48"/>
       <c r="X23" s="48"/>
+      <c r="Y23" s="48"/>
       <c r="Z23" s="48"/>
-      <c r="AC23" s="1"/>
-      <c r="AD23" s="1"/>
+      <c r="AB23" s="48"/>
       <c r="AE23" s="1"/>
       <c r="AF23" s="1"/>
-    </row>
-    <row r="24" spans="1:32">
+      <c r="AG23" s="1"/>
+      <c r="AH23" s="1"/>
+    </row>
+    <row r="24" spans="1:34">
       <c r="A24" s="1"/>
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
@@ -1786,14 +1846,16 @@
       <c r="G24" s="1"/>
       <c r="H24" s="1"/>
       <c r="I24" s="1"/>
-      <c r="N24" s="47"/>
-      <c r="O24" s="47"/>
-      <c r="AC24" s="1"/>
-      <c r="AD24" s="1"/>
+      <c r="J24" s="1"/>
+      <c r="K24" s="1"/>
+      <c r="P24" s="47"/>
+      <c r="Q24" s="47"/>
       <c r="AE24" s="1"/>
       <c r="AF24" s="1"/>
-    </row>
-    <row r="25" spans="1:32">
+      <c r="AG24" s="1"/>
+      <c r="AH24" s="1"/>
+    </row>
+    <row r="25" spans="1:34">
       <c r="A25" s="1"/>
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
@@ -1803,16 +1865,18 @@
       <c r="G25" s="1"/>
       <c r="H25" s="1"/>
       <c r="I25" s="1"/>
-      <c r="N25" s="47"/>
-      <c r="O25" s="47"/>
-      <c r="U25" s="47"/>
-      <c r="V25" s="47"/>
-      <c r="AC25" s="1"/>
-      <c r="AD25" s="1"/>
+      <c r="J25" s="1"/>
+      <c r="K25" s="1"/>
+      <c r="P25" s="47"/>
+      <c r="Q25" s="47"/>
+      <c r="W25" s="47"/>
+      <c r="X25" s="47"/>
       <c r="AE25" s="1"/>
       <c r="AF25" s="1"/>
-    </row>
-    <row r="26" spans="1:32">
+      <c r="AG25" s="1"/>
+      <c r="AH25" s="1"/>
+    </row>
+    <row r="26" spans="1:34">
       <c r="A26" s="1"/>
       <c r="B26" s="1"/>
       <c r="C26" s="1"/>
@@ -1822,16 +1886,18 @@
       <c r="G26" s="1"/>
       <c r="H26" s="1"/>
       <c r="I26" s="1"/>
-      <c r="N26" s="47"/>
-      <c r="O26" s="47"/>
-      <c r="U26" s="47"/>
-      <c r="V26" s="47"/>
-      <c r="AC26" s="1"/>
-      <c r="AD26" s="1"/>
+      <c r="J26" s="1"/>
+      <c r="K26" s="1"/>
+      <c r="P26" s="47"/>
+      <c r="Q26" s="47"/>
+      <c r="W26" s="47"/>
+      <c r="X26" s="47"/>
       <c r="AE26" s="1"/>
       <c r="AF26" s="1"/>
-    </row>
-    <row r="27" spans="1:32">
+      <c r="AG26" s="1"/>
+      <c r="AH26" s="1"/>
+    </row>
+    <row r="27" spans="1:34">
       <c r="A27" s="1"/>
       <c r="B27" s="1"/>
       <c r="C27" s="1"/>
@@ -1841,16 +1907,18 @@
       <c r="G27" s="1"/>
       <c r="H27" s="1"/>
       <c r="I27" s="1"/>
-      <c r="N27" s="47"/>
-      <c r="O27" s="47"/>
-      <c r="U27" s="47"/>
-      <c r="V27" s="47"/>
-      <c r="AC27" s="1"/>
-      <c r="AD27" s="1"/>
+      <c r="J27" s="1"/>
+      <c r="K27" s="1"/>
+      <c r="P27" s="47"/>
+      <c r="Q27" s="47"/>
+      <c r="W27" s="47"/>
+      <c r="X27" s="47"/>
       <c r="AE27" s="1"/>
       <c r="AF27" s="1"/>
-    </row>
-    <row r="28" spans="1:32">
+      <c r="AG27" s="1"/>
+      <c r="AH27" s="1"/>
+    </row>
+    <row r="28" spans="1:34">
       <c r="A28" s="1"/>
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
@@ -1860,28 +1928,30 @@
       <c r="G28" s="1"/>
       <c r="H28" s="1"/>
       <c r="I28" s="1"/>
-      <c r="N28" s="47"/>
-      <c r="O28" s="47"/>
-      <c r="U28" s="47"/>
-      <c r="V28" s="47"/>
-      <c r="AC28" s="1"/>
-      <c r="AD28" s="1"/>
+      <c r="J28" s="1"/>
+      <c r="K28" s="1"/>
+      <c r="P28" s="47"/>
+      <c r="Q28" s="47"/>
+      <c r="W28" s="47"/>
+      <c r="X28" s="47"/>
       <c r="AE28" s="1"/>
       <c r="AF28" s="1"/>
+      <c r="AG28" s="1"/>
+      <c r="AH28" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="K9:M13"/>
-    <mergeCell ref="A1:AH1"/>
-    <mergeCell ref="A2:I2"/>
-    <mergeCell ref="N2:P2"/>
-    <mergeCell ref="V2:W2"/>
-    <mergeCell ref="X2:AB2"/>
-    <mergeCell ref="AD2:AH2"/>
-    <mergeCell ref="R2:U2"/>
+    <mergeCell ref="M9:O13"/>
+    <mergeCell ref="A1:AJ1"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="P2:R2"/>
+    <mergeCell ref="X2:Y2"/>
+    <mergeCell ref="Z2:AD2"/>
+    <mergeCell ref="AF2:AJ2"/>
+    <mergeCell ref="T2:W2"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.70069444444444495" right="0.70069444444444495" top="0.75138888888888899" bottom="0.75138888888888899" header="0.29861111111111099" footer="0.29861111111111099"/>
-  <pageSetup paperSize="9" scale="19" fitToHeight="0" orientation="landscape" verticalDpi="180" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="10" fitToHeight="0" orientation="landscape" verticalDpi="180" r:id="rId1"/>
 </worksheet>
 </file>